--- a/results_day2.xlsx
+++ b/results_day2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kokimoto\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ECB69198-9064-4529-8C9E-E1EE4009D3A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E0E67ED2-B4BE-42E4-B411-E372ABB03ED7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -74,16 +74,16 @@
     <t>Bulgaria</t>
   </si>
   <si>
+    <t>BGR213</t>
+  </si>
+  <si>
+    <t>Радослав Радославов</t>
+  </si>
+  <si>
     <t>BGR215</t>
   </si>
   <si>
     <t>Тихомир Иванов</t>
-  </si>
-  <si>
-    <t>BGR213</t>
-  </si>
-  <si>
-    <t>Радослав Радославов</t>
   </si>
   <si>
     <t>BGR210</t>
@@ -664,11 +664,11 @@
         <v>100</v>
       </c>
       <c r="H3" s="4">
-        <v>83.6</v>
+        <v>89</v>
       </c>
       <c r="I3" s="4">
-        <f t="shared" ref="I3:I18" si="0">SUM(E3:H3)</f>
-        <v>383.6</v>
+        <f>SUM(E3:H3)</f>
+        <v>389</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15">
@@ -694,11 +694,11 @@
         <v>100</v>
       </c>
       <c r="H4" s="4">
-        <v>50.4</v>
+        <v>83.6</v>
       </c>
       <c r="I4" s="4">
-        <f t="shared" si="0"/>
-        <v>350.4</v>
+        <f>SUM(E4:H4)</f>
+        <v>383.6</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15">
@@ -727,7 +727,7 @@
         <v>35</v>
       </c>
       <c r="I5" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="I5:I18" si="0">SUM(E5:H5)</f>
         <v>335</v>
       </c>
     </row>
